--- a/baselines/BASELINE_v7_WC_GL_PR.xlsx
+++ b/baselines/BASELINE_v7_WC_GL_PR.xlsx
@@ -1294,13 +1294,13 @@
         <v>Invested Assets</v>
       </c>
       <c r="C53">
-        <v>51175069</v>
+        <v>51006853</v>
       </c>
       <c r="D53">
-        <v>59115912</v>
+        <v>58882149</v>
       </c>
       <c r="E53">
-        <v>67626445</v>
+        <v>66119262</v>
       </c>
     </row>
     <row r="54">
@@ -1311,13 +1311,13 @@
         <v>Investment Return Rate</v>
       </c>
       <c r="C54">
-        <v>0.031028774529870885</v>
+        <v>0.029846044611871382</v>
       </c>
       <c r="D54">
-        <v>0.048108093605185864</v>
+        <v>0.026672499855790524</v>
       </c>
       <c r="E54">
-        <v>0.03517632219622337</v>
+        <v>0.027616823897519745</v>
       </c>
     </row>
     <row r="55">
@@ -1328,13 +1328,13 @@
         <v>Investment Income</v>
       </c>
       <c r="C55">
-        <v>1587900</v>
+        <v>1522353</v>
       </c>
       <c r="D55">
-        <v>2843954</v>
+        <v>1570534</v>
       </c>
       <c r="E55">
-        <v>2378850</v>
+        <v>1826004</v>
       </c>
     </row>
     <row r="56">
@@ -1345,13 +1345,13 @@
         <v>Net Income</v>
       </c>
       <c r="C56">
-        <v>4550489</v>
+        <v>4484942</v>
       </c>
       <c r="D56">
-        <v>5419371</v>
+        <v>4145952</v>
       </c>
       <c r="E56">
-        <v>12425834</v>
+        <v>11872988</v>
       </c>
     </row>
     <row r="57">
@@ -1566,13 +1566,13 @@
         <v>Beginning Investments</v>
       </c>
       <c r="C69">
-        <v>51175069</v>
+        <v>51006853</v>
       </c>
       <c r="D69">
-        <v>59115912</v>
+        <v>58882149</v>
       </c>
       <c r="E69">
-        <v>67626445</v>
+        <v>66119262</v>
       </c>
     </row>
     <row r="70">
@@ -1583,13 +1583,13 @@
         <v>Ending Investments</v>
       </c>
       <c r="C70">
-        <v>59115912</v>
+        <v>58882149</v>
       </c>
       <c r="D70">
-        <v>67626445</v>
+        <v>66119262</v>
       </c>
       <c r="E70">
-        <v>77950707</v>
+        <v>75890678</v>
       </c>
     </row>
     <row r="71">
@@ -1617,13 +1617,13 @@
         <v>Total Assets</v>
       </c>
       <c r="C72">
-        <v>66082320</v>
+        <v>65848557</v>
       </c>
       <c r="D72">
-        <v>74669320</v>
+        <v>73162137</v>
       </c>
       <c r="E72">
-        <v>84818366</v>
+        <v>82758337</v>
       </c>
     </row>
     <row r="73">
@@ -1685,13 +1685,13 @@
         <v>Beginning Surplus</v>
       </c>
       <c r="C76">
-        <v>36701664</v>
+        <v>36533447</v>
       </c>
       <c r="D76">
-        <v>41252153</v>
+        <v>41018389</v>
       </c>
       <c r="E76">
-        <v>46671524</v>
+        <v>45164341</v>
       </c>
     </row>
     <row r="77">
@@ -1702,13 +1702,13 @@
         <v>Surplus from Income</v>
       </c>
       <c r="C77">
-        <v>41252153</v>
+        <v>41018389</v>
       </c>
       <c r="D77">
-        <v>46671524</v>
+        <v>45164341</v>
       </c>
       <c r="E77">
-        <v>59097357</v>
+        <v>57037329</v>
       </c>
     </row>
     <row r="78">
@@ -1719,13 +1719,13 @@
         <v>Ending Surplus</v>
       </c>
       <c r="C78">
-        <v>41252153</v>
+        <v>41018389</v>
       </c>
       <c r="D78">
-        <v>46671524</v>
+        <v>45164341</v>
       </c>
       <c r="E78">
-        <v>59097357</v>
+        <v>57037329</v>
       </c>
     </row>
     <row r="79">
@@ -1923,13 +1923,13 @@
         <v>Surplus</v>
       </c>
       <c r="C90">
-        <v>41252153</v>
+        <v>41018389</v>
       </c>
       <c r="D90">
-        <v>46671524</v>
+        <v>45164341</v>
       </c>
       <c r="E90">
-        <v>59097357</v>
+        <v>57037329</v>
       </c>
     </row>
     <row r="91">
@@ -1940,13 +1940,13 @@
         <v>Excess Available Surplus</v>
       </c>
       <c r="C91">
-        <v>20131543</v>
+        <v>19897779</v>
       </c>
       <c r="D91">
-        <v>22292543</v>
+        <v>20785360</v>
       </c>
       <c r="E91">
-        <v>36479889</v>
+        <v>34419861</v>
       </c>
     </row>
     <row r="92">
@@ -1957,13 +1957,13 @@
         <v>Excess Capital Ratio</v>
       </c>
       <c r="C92">
-        <v>0.9531705046822945</v>
+        <v>0.9421024906314687</v>
       </c>
       <c r="D92">
-        <v>0.9144165328776996</v>
+        <v>0.8525934833550703</v>
       </c>
       <c r="E92">
-        <v>1.612907735891825</v>
+        <v>1.5218264298689612</v>
       </c>
     </row>
     <row r="93">
@@ -3450,10 +3450,10 @@
         <v>1.310957775003503</v>
       </c>
       <c r="D86">
-        <v>0.9955678714097149</v>
+        <v>0.9955678714097158</v>
       </c>
       <c r="E86">
-        <v>1.048957058801614</v>
+        <v>1.0489570588016146</v>
       </c>
     </row>
     <row r="87">
@@ -4274,13 +4274,13 @@
         <v>Invested Assets</v>
       </c>
       <c r="C47">
-        <v>16353214</v>
+        <v>16068522</v>
       </c>
       <c r="D47">
-        <v>18372940</v>
+        <v>18065231</v>
       </c>
       <c r="E47">
-        <v>21220071</v>
+        <v>20113480</v>
       </c>
     </row>
     <row r="48">
@@ -4291,13 +4291,13 @@
         <v>Investment Return Rate</v>
       </c>
       <c r="C48">
-        <v>0.030733996516013377</v>
+        <v>0.029846044611871386</v>
       </c>
       <c r="D48">
-        <v>0.06970720915315894</v>
+        <v>0.02667249985579053</v>
       </c>
       <c r="E48">
-        <v>0.051608526746957165</v>
+        <v>0.027616823897519745</v>
       </c>
     </row>
     <row r="49">
@@ -4308,13 +4308,13 @@
         <v>Investment Income</v>
       </c>
       <c r="C49">
-        <v>502600</v>
+        <v>479582</v>
       </c>
       <c r="D49">
-        <v>1280726</v>
+        <v>481845</v>
       </c>
       <c r="E49">
-        <v>1095137</v>
+        <v>555470</v>
       </c>
     </row>
     <row r="50">
@@ -4325,13 +4325,13 @@
         <v>Net Income</v>
       </c>
       <c r="C50">
-        <v>-95762</v>
+        <v>-118780</v>
       </c>
       <c r="D50">
-        <v>2017457</v>
+        <v>1218576</v>
       </c>
       <c r="E50">
-        <v>6253646</v>
+        <v>5713980</v>
       </c>
     </row>
     <row r="51">
@@ -4546,13 +4546,13 @@
         <v>Beginning Investments</v>
       </c>
       <c r="C63">
-        <v>16353214</v>
+        <v>16068522</v>
       </c>
       <c r="D63">
-        <v>18372940</v>
+        <v>18065231</v>
       </c>
       <c r="E63">
-        <v>21220071</v>
+        <v>20113480</v>
       </c>
     </row>
     <row r="64">
@@ -4563,13 +4563,13 @@
         <v>Ending Investments</v>
       </c>
       <c r="C64">
-        <v>18372940</v>
+        <v>18065231</v>
       </c>
       <c r="D64">
-        <v>21220071</v>
+        <v>20113480</v>
       </c>
       <c r="E64">
-        <v>25571883</v>
+        <v>23925626</v>
       </c>
     </row>
     <row r="65">
@@ -4597,13 +4597,13 @@
         <v>Total Assets</v>
       </c>
       <c r="C66">
-        <v>21828425</v>
+        <v>21520715</v>
       </c>
       <c r="D66">
-        <v>24309161</v>
+        <v>23202570</v>
       </c>
       <c r="E66">
-        <v>28458738</v>
+        <v>26812481</v>
       </c>
     </row>
     <row r="67">
@@ -4665,13 +4665,13 @@
         <v>Beginning Surplus</v>
       </c>
       <c r="C70">
-        <v>9310013</v>
+        <v>9025321</v>
       </c>
       <c r="D70">
-        <v>9214250</v>
+        <v>8906541</v>
       </c>
       <c r="E70">
-        <v>11231708</v>
+        <v>10125117</v>
       </c>
     </row>
     <row r="71">
@@ -4682,13 +4682,13 @@
         <v>Surplus from Income</v>
       </c>
       <c r="C71">
-        <v>9214250</v>
+        <v>8906541</v>
       </c>
       <c r="D71">
-        <v>11231708</v>
+        <v>10125117</v>
       </c>
       <c r="E71">
-        <v>17485354</v>
+        <v>15839097</v>
       </c>
     </row>
     <row r="72">
@@ -4699,13 +4699,13 @@
         <v>Ending Surplus</v>
       </c>
       <c r="C72">
-        <v>9214250</v>
+        <v>8906541</v>
       </c>
       <c r="D72">
-        <v>11231708</v>
+        <v>10125117</v>
       </c>
       <c r="E72">
-        <v>17485354</v>
+        <v>15839097</v>
       </c>
     </row>
     <row r="73">
@@ -4903,13 +4903,13 @@
         <v>Surplus</v>
       </c>
       <c r="C84">
-        <v>9214250</v>
+        <v>8906541</v>
       </c>
       <c r="D84">
-        <v>11231708</v>
+        <v>10125117</v>
       </c>
       <c r="E84">
-        <v>17485354</v>
+        <v>15839097</v>
       </c>
     </row>
     <row r="85">
@@ -4920,13 +4920,13 @@
         <v>Excess Available Surplus</v>
       </c>
       <c r="C85">
-        <v>-1041848</v>
+        <v>-1349558</v>
       </c>
       <c r="D85">
-        <v>65731</v>
+        <v>-1040860</v>
       </c>
       <c r="E85">
-        <v>8055556</v>
+        <v>6409298</v>
       </c>
     </row>
     <row r="86">
@@ -4937,13 +4937,13 @@
         <v>Excess Capital Ratio</v>
       </c>
       <c r="C86">
-        <v>-0.10158327615482844</v>
+        <v>-0.1315858760846422</v>
       </c>
       <c r="D86">
-        <v>0.005886710193914888</v>
+        <v>-0.09321712764259381</v>
       </c>
       <c r="E86">
-        <v>0.8542659824252907</v>
+        <v>0.6796856467751696</v>
       </c>
     </row>
     <row r="87">
@@ -4957,7 +4957,7 @@
         <v>Deficient</v>
       </c>
       <c r="D87" t="str">
-        <v>Adequate</v>
+        <v>Thin</v>
       </c>
       <c r="E87" t="str">
         <v>Strong</v>
@@ -5764,13 +5764,13 @@
         <v>Invested Assets</v>
       </c>
       <c r="C47">
-        <v>14036260</v>
+        <v>14152736</v>
       </c>
       <c r="D47">
-        <v>16858906</v>
+        <v>16932852</v>
       </c>
       <c r="E47">
-        <v>20057455</v>
+        <v>19656863</v>
       </c>
     </row>
     <row r="48">
@@ -5781,13 +5781,13 @@
         <v>Investment Return Rate</v>
       </c>
       <c r="C48">
-        <v>0.033123656762734995</v>
+        <v>0.029846044611871386</v>
       </c>
       <c r="D48">
-        <v>0.054937118165149956</v>
+        <v>0.02667249985579053</v>
       </c>
       <c r="E48">
-        <v>0.027722338606643512</v>
+        <v>0.027616823897519745</v>
       </c>
     </row>
     <row r="49">
@@ -5798,13 +5798,13 @@
         <v>Investment Income</v>
       </c>
       <c r="C49">
-        <v>464932</v>
+        <v>422403</v>
       </c>
       <c r="D49">
-        <v>926180</v>
+        <v>451641</v>
       </c>
       <c r="E49">
-        <v>556040</v>
+        <v>542860</v>
       </c>
     </row>
     <row r="50">
@@ -5815,13 +5815,13 @@
         <v>Net Income</v>
       </c>
       <c r="C50">
-        <v>2914903</v>
+        <v>2872374</v>
       </c>
       <c r="D50">
-        <v>2548661</v>
+        <v>2074123</v>
       </c>
       <c r="E50">
-        <v>4225492</v>
+        <v>4212312</v>
       </c>
     </row>
     <row r="51">
@@ -6036,13 +6036,13 @@
         <v>Beginning Investments</v>
       </c>
       <c r="C63">
-        <v>14036260</v>
+        <v>14152736</v>
       </c>
       <c r="D63">
-        <v>16858906</v>
+        <v>16932852</v>
       </c>
       <c r="E63">
-        <v>20057455</v>
+        <v>19656863</v>
       </c>
     </row>
     <row r="64">
@@ -6053,13 +6053,13 @@
         <v>Ending Investments</v>
       </c>
       <c r="C64">
-        <v>16858906</v>
+        <v>16932852</v>
       </c>
       <c r="D64">
-        <v>20057455</v>
+        <v>19656863</v>
       </c>
       <c r="E64">
-        <v>23432766</v>
+        <v>23018995</v>
       </c>
     </row>
     <row r="65">
@@ -6087,13 +6087,13 @@
         <v>Total Assets</v>
       </c>
       <c r="C66">
-        <v>18405233</v>
+        <v>18479179</v>
       </c>
       <c r="D66">
-        <v>21720220</v>
+        <v>21319628</v>
       </c>
       <c r="E66">
-        <v>25175186</v>
+        <v>24761415</v>
       </c>
     </row>
     <row r="67">
@@ -6155,13 +6155,13 @@
         <v>Beginning Surplus</v>
       </c>
       <c r="C70">
-        <v>11699003</v>
+        <v>11815478</v>
       </c>
       <c r="D70">
-        <v>14613906</v>
+        <v>14687853</v>
       </c>
       <c r="E70">
-        <v>17162567</v>
+        <v>16761975</v>
       </c>
     </row>
     <row r="71">
@@ -6172,13 +6172,13 @@
         <v>Surplus from Income</v>
       </c>
       <c r="C71">
-        <v>14613906</v>
+        <v>14687853</v>
       </c>
       <c r="D71">
-        <v>17162567</v>
+        <v>16761975</v>
       </c>
       <c r="E71">
-        <v>21388059</v>
+        <v>20974288</v>
       </c>
     </row>
     <row r="72">
@@ -6189,13 +6189,13 @@
         <v>Ending Surplus</v>
       </c>
       <c r="C72">
-        <v>14613906</v>
+        <v>14687853</v>
       </c>
       <c r="D72">
-        <v>17162567</v>
+        <v>16761975</v>
       </c>
       <c r="E72">
-        <v>21388059</v>
+        <v>20974288</v>
       </c>
     </row>
     <row r="73">
@@ -6393,13 +6393,13 @@
         <v>Surplus</v>
       </c>
       <c r="C84">
-        <v>14613906</v>
+        <v>14687853</v>
       </c>
       <c r="D84">
-        <v>17162567</v>
+        <v>16761975</v>
       </c>
       <c r="E84">
-        <v>21388059</v>
+        <v>20974288</v>
       </c>
     </row>
     <row r="85">
@@ -6410,13 +6410,13 @@
         <v>Excess Available Surplus</v>
       </c>
       <c r="C85">
-        <v>11289124</v>
+        <v>11363070</v>
       </c>
       <c r="D85">
-        <v>13108484</v>
+        <v>12707893</v>
       </c>
       <c r="E85">
-        <v>18070749</v>
+        <v>17656978</v>
       </c>
     </row>
     <row r="86">
@@ -6427,13 +6427,13 @@
         <v>Excess Capital Ratio</v>
       </c>
       <c r="C86">
-        <v>3.395447648068545</v>
+        <v>3.417688627672162</v>
       </c>
       <c r="D86">
-        <v>3.2334032915630777</v>
+        <v>3.134591350930385</v>
       </c>
       <c r="E86">
-        <v>5.447411043969138</v>
+        <v>5.322680086974258</v>
       </c>
     </row>
     <row r="87">

--- a/baselines/BASELINE_v7_WC_GL_PR.xlsx
+++ b/baselines/BASELINE_v7_WC_GL_PR.xlsx
@@ -410,13 +410,13 @@
         <v>Metric</v>
       </c>
       <c r="C1" t="str">
-        <v>Year 1 / 2025</v>
+        <v>Year 1 / 2026</v>
       </c>
       <c r="D1" t="str">
-        <v>Year 2 / 2026</v>
+        <v>Year 2 / 2027</v>
       </c>
       <c r="E1" t="str">
-        <v>Year 3 / 2027</v>
+        <v>Year 3 / 2028</v>
       </c>
     </row>
     <row r="2">
@@ -444,13 +444,13 @@
         <v>Calendar Year</v>
       </c>
       <c r="C3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D3">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E3">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="4">
@@ -1314,7 +1314,7 @@
         <v>0.029846044611871382</v>
       </c>
       <c r="D54">
-        <v>0.026672499855790524</v>
+        <v>0.026672499855790528</v>
       </c>
       <c r="E54">
         <v>0.027616823897519745</v>
@@ -1957,10 +1957,10 @@
         <v>Excess Capital Ratio</v>
       </c>
       <c r="C92">
-        <v>0.9421024906314687</v>
+        <v>0.9421024906314684</v>
       </c>
       <c r="D92">
-        <v>0.8525934833550703</v>
+        <v>0.8525934833550701</v>
       </c>
       <c r="E92">
         <v>1.5218264298689612</v>
@@ -2002,13 +2002,13 @@
         <v>Metric</v>
       </c>
       <c r="C1" t="str">
-        <v>Year 1 / 2025</v>
+        <v>Year 1 / 2026</v>
       </c>
       <c r="D1" t="str">
-        <v>Year 2 / 2026</v>
+        <v>Year 2 / 2027</v>
       </c>
       <c r="E1" t="str">
-        <v>Year 3 / 2027</v>
+        <v>Year 3 / 2028</v>
       </c>
     </row>
     <row r="2">
@@ -2036,13 +2036,13 @@
         <v>Calendar Year</v>
       </c>
       <c r="C3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D3">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E3">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="4">
@@ -3492,13 +3492,13 @@
         <v>Metric</v>
       </c>
       <c r="C1" t="str">
-        <v>Year 1 / 2025</v>
+        <v>Year 1 / 2026</v>
       </c>
       <c r="D1" t="str">
-        <v>Year 2 / 2026</v>
+        <v>Year 2 / 2027</v>
       </c>
       <c r="E1" t="str">
-        <v>Year 3 / 2027</v>
+        <v>Year 3 / 2028</v>
       </c>
     </row>
     <row r="2">
@@ -3526,13 +3526,13 @@
         <v>Calendar Year</v>
       </c>
       <c r="C3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D3">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E3">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="4">
@@ -4982,13 +4982,13 @@
         <v>Metric</v>
       </c>
       <c r="C1" t="str">
-        <v>Year 1 / 2025</v>
+        <v>Year 1 / 2026</v>
       </c>
       <c r="D1" t="str">
-        <v>Year 2 / 2026</v>
+        <v>Year 2 / 2027</v>
       </c>
       <c r="E1" t="str">
-        <v>Year 3 / 2027</v>
+        <v>Year 3 / 2028</v>
       </c>
     </row>
     <row r="2">
@@ -5016,13 +5016,13 @@
         <v>Calendar Year</v>
       </c>
       <c r="C3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D3">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E3">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="4">
@@ -6427,10 +6427,10 @@
         <v>Excess Capital Ratio</v>
       </c>
       <c r="C86">
-        <v>3.417688627672162</v>
+        <v>3.4176886276721605</v>
       </c>
       <c r="D86">
-        <v>3.134591350930385</v>
+        <v>3.134591350930384</v>
       </c>
       <c r="E86">
         <v>5.322680086974258</v>
